--- a/Macro Inv Tarde/VALORIZADO TOBERIN.xlsx
+++ b/Macro Inv Tarde/VALORIZADO TOBERIN.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t>Categoría</t>
   </si>
@@ -55,21 +55,33 @@
     <t>Categoría producto</t>
   </si>
   <si>
+    <t>Categoría producto importación</t>
+  </si>
+  <si>
     <t>BA403008</t>
   </si>
   <si>
+    <t>WAB9650011030</t>
+  </si>
+  <si>
     <t>4515/C/X/WI 700</t>
   </si>
   <si>
     <t>DANA</t>
   </si>
   <si>
+    <t>WABCO</t>
+  </si>
+  <si>
     <t>FRAS-LE</t>
   </si>
   <si>
     <t>KIT SPLINDER AGRALE 170MM x 33MM</t>
   </si>
   <si>
+    <t>PEDAL CLUTCH M2-106  M2-112 COLUMBIA CARRERA O DESPLAZAMIENTO 194 MM</t>
+  </si>
+  <si>
     <t>BLOQUE TRASERA Y TRAILER (1 JG VIENE X 8 BLOQUES) PARA MACK  R600 -R700/CHEVOLET SUPER BRIGARDIER, KODIAK/ BRIGADIER / DODGE 600 f /INTERNATIONAL 4300-HI-HI500 / FORD F800,FT9000 FREIGHTLINER/MACK/ROMARCO TRAILER  (solo si la zapata tiene 7 pulgadas de ancho)/DITE TRAILER/INCA FRUEHAUE TRAILER</t>
   </si>
   <si>
@@ -91,13 +103,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 09:44:16</t>
+    <t>Período: 30/11/2025 13:41:04</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 23/10/2025 09:45:06</t>
+    <t>Fecha y hora de generación: 05/11/2025 13:41:26</t>
   </si>
 </sst>
 </file>
@@ -511,28 +523,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -548,7 +560,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -564,12 +576,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -618,22 +630,22 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
         <v>17</v>
       </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -647,34 +659,66 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11">
+        <v>59</v>
+      </c>
+      <c r="K11">
+        <v>1268236.6</v>
+      </c>
+      <c r="L11">
+        <v>74825959.40000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="C12" t="s">
         <v>19</v>
       </c>
-      <c r="J11">
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12">
         <v>24</v>
       </c>
-      <c r="K11">
-        <v>105339.15</v>
-      </c>
-      <c r="L11">
-        <v>2528139.6</v>
+      <c r="K12">
+        <v>103344.83</v>
+      </c>
+      <c r="L12">
+        <v>2480275.92</v>
       </c>
     </row>
   </sheetData>

--- a/Macro Inv Tarde/VALORIZADO TOBERIN.xlsx
+++ b/Macro Inv Tarde/VALORIZADO TOBERIN.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="54">
   <si>
     <t>Categoría</t>
   </si>
@@ -55,24 +55,102 @@
     <t>Categoría producto</t>
   </si>
   <si>
+    <t>Categoría producto importación</t>
+  </si>
+  <si>
     <t>BA403008</t>
   </si>
   <si>
+    <t>WAB9650011030</t>
+  </si>
+  <si>
     <t>4515/C/X/WI 700</t>
   </si>
   <si>
+    <t>4515/C/WI 557</t>
+  </si>
+  <si>
+    <t>4707/WI700</t>
+  </si>
+  <si>
+    <t>4707/X/WI700</t>
+  </si>
+  <si>
+    <t>4707/WI557</t>
+  </si>
+  <si>
+    <t>4709/WI700</t>
+  </si>
+  <si>
+    <t>4720/WI700</t>
+  </si>
+  <si>
+    <t>4715/WI700</t>
+  </si>
+  <si>
+    <t>4709/X/WI557</t>
+  </si>
+  <si>
+    <t>CA/32/X/WI557</t>
+  </si>
+  <si>
+    <t>700078C-01-E</t>
+  </si>
+  <si>
+    <t>4715/X/WI700</t>
+  </si>
+  <si>
     <t>DANA</t>
   </si>
   <si>
+    <t>WABCO</t>
+  </si>
+  <si>
     <t>FRAS-LE</t>
   </si>
   <si>
     <t>KIT SPLINDER AGRALE 170MM x 33MM</t>
   </si>
   <si>
+    <t>PEDAL CLUTCH M2-106  M2-112 COLUMBIA CARRERA O DESPLAZAMIENTO 194 MM</t>
+  </si>
+  <si>
     <t>BLOQUE TRASERA Y TRAILER (1 JG VIENE X 8 BLOQUES) PARA MACK  R600 -R700/CHEVOLET SUPER BRIGARDIER, KODIAK/ BRIGADIER / DODGE 600 f /INTERNATIONAL 4300-HI-HI500 / FORD F800,FT9000 FREIGHTLINER/MACK/ROMARCO TRAILER  (solo si la zapata tiene 7 pulgadas de ancho)/DITE TRAILER/INCA FRUEHAUE TRAILER</t>
   </si>
   <si>
+    <t>BLOQUE TRASERA Y TRAILER (1 JG VIENE X 8 BLOQUES) PARA MACK  R600 -R700/CHEVOLET SUPER BRIGARDIER, KODIAK/ BRIGADIER / DODGE 600 f /INTERNATIONAL 4300-HI-HI500 / FORD F800,FT9000 FREIGHTLINER/MACK/ROMARCO TRAILER (solo si la zapata tiene 7 pulgadas de ancho)/DITE TRAILER/INCA FRUEHAUE TRAILER</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERO  (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-112</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-113</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA KENWORTH T300-T800/MACK CT713INTERNATIONAL 4700 -4300-7600/ ROCKWELL AXLE / FREIGHTLINER M2 106-112</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERA (1 JG VIENE X 8 BLOQUES) PARA INTERNATIONAL 9400--9900/EATON BRAKES 16.5" DIA. X 7" /MERCEDES CAMION CLASE7 / KENWORTH T600,T800 EJE EATON MODELO 2002-2007-CAMION 7600 INTER</t>
+  </si>
+  <si>
+    <t>BLOQUE DELANTERO (1 JG VIENE X 8 BLOQUES) PARA FREIGHTLINER  COLUMBIA-M2 106 -112 -CASCADIA/INTERNATIONAL  7600-4300-PROSTAR/ KENWORTH T800, MERITOR TAMBOR DIA 16,5" X ANCHO 5"/ COMPAÑERO CON EL 4707</t>
+  </si>
+  <si>
+    <t>BLOQUE DELANTERO (1 JG VIENE X 8 BLOQUES) PARA FORD F-800/INTERNATIONAL 4700, 9400 TAMBOR DIA 16.5" X 6 " ANCHO /EJE ROCKWELL./BLUE BIRD./FRENO DELANTERO BOLQUETA INTERNATIONAL 7600</t>
+  </si>
+  <si>
+    <t>BLOQUE TRASERA CON SOBRE MEDIDA PARA INTERNATIONAL 9400--9900/EATON BRAKES 16.5" DIA. X 7" /MERCEDES CAMION CLASE7 / KENWORTH T600,T800 EJE EATON MODELO 2002-2007-CAMION 7600 INTER./1 JUEGO TIENE 8 BLOQUES; (KENWORTH T800 PARA EJE MARCA DANA) VENTA MINIMA 1 CAJA QUE TRAE 2 JUEGOS (16 BLOQUES) EL PRECIO DE LISTA ES POR 1 JUEGO</t>
+  </si>
+  <si>
+    <t>BLOQUE TRAILER (CON SOBRE MEDIDA .86 MILESIMAS DE PULGADA MAS GRUESO) PARA ROMARCO CAMPANA DIAM "16.5 x 8" ANCHO</t>
+  </si>
+  <si>
+    <t>REMACHE ACERADO 10-8 SEMI TUBULAR PARA BANDA PERFORADA (PAQUETE POR MILLAR)</t>
+  </si>
+  <si>
+    <t>BLOQUE DELANTERO(CON SOBRE MEDIDA .86 MILESIMAS DE PULGADA MAS GRUESO) PARA INTERNATIONAL WORKSTAR, 4700, 9400  FORD F-800/TAMBOR DIA 16.5" X 6 " ANCHO /EJE ROCKWELL./BLUE BIRD./FRENO DELANTERO VOLQUETA INTERNATIONAL 7600</t>
+  </si>
+  <si>
     <t>Unidad</t>
   </si>
   <si>
@@ -91,13 +169,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 09:44:16</t>
+    <t>Período: 30/11/2025 12:35:17</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 23/10/2025 09:45:06</t>
+    <t>Fecha y hora de generación: 04/11/2025 12:35:34</t>
   </si>
 </sst>
 </file>
@@ -511,28 +589,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -548,7 +626,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -564,12 +642,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -618,22 +696,22 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -647,34 +725,418 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11">
+        <v>59</v>
+      </c>
+      <c r="K11">
+        <v>1268236.6</v>
+      </c>
+      <c r="L11">
+        <v>74825959.40000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12">
+        <v>354</v>
+      </c>
+      <c r="K12">
+        <v>103344.83</v>
+      </c>
+      <c r="L12">
+        <v>36584069.82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13">
+        <v>24</v>
+      </c>
+      <c r="K13">
+        <v>117534.05</v>
+      </c>
+      <c r="L13">
+        <v>2820817.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
         <v>18</v>
       </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14">
+        <v>60</v>
+      </c>
+      <c r="K14">
+        <v>113167.54</v>
+      </c>
+      <c r="L14">
+        <v>6790052.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
         <v>19</v>
       </c>
-      <c r="J11">
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>118404.06</v>
+      </c>
+      <c r="L15">
+        <v>1776060.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J16">
+        <v>60</v>
+      </c>
+      <c r="K16">
+        <v>124047</v>
+      </c>
+      <c r="L16">
+        <v>7442820</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17">
+        <v>180</v>
+      </c>
+      <c r="K17">
+        <v>113701.69</v>
+      </c>
+      <c r="L17">
+        <v>20466304.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18">
+        <v>32</v>
+      </c>
+      <c r="K18">
+        <v>81253.13</v>
+      </c>
+      <c r="L18">
+        <v>2600100.16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" t="s">
+        <v>45</v>
+      </c>
+      <c r="J19">
+        <v>6</v>
+      </c>
+      <c r="K19">
+        <v>98376.67</v>
+      </c>
+      <c r="L19">
+        <v>590260.02</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
         <v>24</v>
       </c>
-      <c r="K11">
-        <v>105339.15</v>
-      </c>
-      <c r="L11">
-        <v>2528139.6</v>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" t="s">
+        <v>45</v>
+      </c>
+      <c r="J20">
+        <v>4</v>
+      </c>
+      <c r="K20">
+        <v>159095</v>
+      </c>
+      <c r="L20">
+        <v>636380</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21">
+        <v>50</v>
+      </c>
+      <c r="K21">
+        <v>132600</v>
+      </c>
+      <c r="L21">
+        <v>6630000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22">
+        <v>18</v>
+      </c>
+      <c r="K22">
+        <v>120464.5</v>
+      </c>
+      <c r="L22">
+        <v>2168361</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" t="s">
+        <v>45</v>
+      </c>
+      <c r="J23">
+        <v>12</v>
+      </c>
+      <c r="K23">
+        <v>125228</v>
+      </c>
+      <c r="L23">
+        <v>1502736</v>
       </c>
     </row>
   </sheetData>

--- a/Macro Inv Tarde/VALORIZADO TOBERIN.xlsx
+++ b/Macro Inv Tarde/VALORIZADO TOBERIN.xlsx
@@ -103,13 +103,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 30/11/2025 13:41:04</t>
+    <t>Período: 30/11/2025 13:21:00</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 05/11/2025 13:41:26</t>
+    <t>Fecha y hora de generación: 06/11/2025 13:21:20</t>
   </si>
 </sst>
 </file>
